--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run8/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="511">
   <si>
     <t>Filename</t>
   </si>
@@ -808,733 +808,745 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.9220,0.0004,0.0995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0487,0.0002,0.0492,0.8950</t>
-  </si>
-  <si>
-    <t>0.9282,0.0006,0.0540,0.0012</t>
-  </si>
-  <si>
-    <t>0.1767,0.0001,0.1654,0.3289</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9330,0.0004,0.0794,0.0002</t>
+  </si>
+  <si>
+    <t>0.6674,0.0003,0.0481,0.0934</t>
+  </si>
+  <si>
+    <t>0.9805,0.0004,0.0090,0.0005</t>
+  </si>
+  <si>
+    <t>0.2375,0.0005,0.1551,0.3993</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0021,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8668,0.0002,0.2440,0.0000</t>
+  </si>
+  <si>
+    <t>0.0510,0.0003,0.9675,0.0001</t>
+  </si>
+  <si>
+    <t>0.7937,0.0005,0.3471,0.0001</t>
+  </si>
+  <si>
+    <t>0.1238,0.0003,0.9416,0.0001</t>
+  </si>
+  <si>
+    <t>0.7182,0.0003,0.4642,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9982,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.1116,0.9113,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.8593,0.1191,0.0051,0.0001</t>
+  </si>
+  <si>
+    <t>0.0387,0.9742,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9984,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9315,0.0002,0.1015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9043,0.0000,0.1982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0119,0.0001,0.9895,0.0004</t>
+  </si>
+  <si>
+    <t>0.0980,0.0001,0.9474,0.0001</t>
+  </si>
+  <si>
+    <t>0.0195,0.0001,0.9914,0.0000</t>
+  </si>
+  <si>
+    <t>0.1020,0.0001,0.9484,0.0002</t>
+  </si>
+  <si>
+    <t>0.0053,0.0001,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.6884,0.3303,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9765,0.0016,0.0116,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0010,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.2476,0.1217,0.3558,0.0001</t>
+  </si>
+  <si>
+    <t>0.9911,0.0006,0.0022,0.0002</t>
+  </si>
+  <si>
+    <t>0.3699,0.0028,0.7357,0.0002</t>
+  </si>
+  <si>
+    <t>0.9339,0.0207,0.0175,0.0003</t>
+  </si>
+  <si>
+    <t>0.4072,0.4122,0.0498,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.9680,0.3699,0.0005</t>
+  </si>
+  <si>
+    <t>0.5351,0.0009,0.6012,0.0004</t>
+  </si>
+  <si>
+    <t>0.0165,0.2400,0.9189,0.0003</t>
+  </si>
+  <si>
+    <t>0.7433,0.0001,0.5110,0.0000</t>
+  </si>
+  <si>
+    <t>0.1013,0.0412,0.8466,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.9960,0.0113,0.0001</t>
+  </si>
+  <si>
+    <t>0.0164,0.0004,0.9897,0.0000</t>
+  </si>
+  <si>
+    <t>0.4552,0.3609,0.0548,0.0393</t>
+  </si>
+  <si>
+    <t>0.0015,0.9962,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.0007,0.9975,0.0019,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0025,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0756,0.9896,0.0000</t>
+  </si>
+  <si>
+    <t>0.0380,0.0004,0.9735,0.0001</t>
+  </si>
+  <si>
+    <t>0.0061,0.0000,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0064,0.0006,0.9958,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0031,0.9974,0.0001</t>
+  </si>
+  <si>
+    <t>0.9948,0.0053,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0018,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9457,0.0224,0.0119,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0073,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.9978,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9943,0.0063,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9888,0.0116,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9700,0.9490,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0012,0.9987,0.0000</t>
+  </si>
+  <si>
+    <t>0.0222,0.0035,0.9773,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9892,0.9773,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0999,0.8593,0.0060,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9412,0.0007,0.0652,0.0001</t>
+  </si>
+  <si>
+    <t>0.7357,0.0005,0.4430,0.0001</t>
+  </si>
+  <si>
+    <t>0.0207,0.0125,0.9754,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9760,0.9871,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9562,0.3540,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.0363,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9938,0.3829,0.0000</t>
+  </si>
+  <si>
+    <t>0.0839,0.0004,0.1302,0.6392</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.0007,0.9992</t>
+  </si>
+  <si>
+    <t>0.1617,0.0002,0.0007,0.9410</t>
+  </si>
+  <si>
+    <t>0.0052,0.0003,0.4705,0.8768</t>
+  </si>
+  <si>
+    <t>0.0033,0.0001,0.2070,0.9583</t>
+  </si>
+  <si>
+    <t>0.0034,0.0002,0.0886,0.9754</t>
+  </si>
+  <si>
+    <t>0.0002,0.9958,0.0906,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9820,0.6159,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9417,0.6228,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.4933,0.9485,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9841,0.8564,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9106,0.9602,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9939,0.0034,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9834,0.0146,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0022,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0014,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9947,0.0062,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0013,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0752,0.0012,0.9626,0.0001</t>
+  </si>
+  <si>
+    <t>0.3327,0.0013,0.8197,0.0001</t>
+  </si>
+  <si>
+    <t>0.9700,0.0005,0.0214,0.0001</t>
+  </si>
+  <si>
+    <t>0.0157,0.0001,0.9938,0.0000</t>
+  </si>
+  <si>
+    <t>0.0199,0.9800,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0306,0.9662,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.1343,0.9064,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.2679,0.7466,0.0085,0.0003</t>
+  </si>
+  <si>
+    <t>0.0034,0.9953,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0044,0.9920,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.7961,0.2398,0.0036,0.0001</t>
+  </si>
+  <si>
+    <t>0.4971,0.0052,0.5913,0.0004</t>
+  </si>
+  <si>
+    <t>0.6819,0.0003,0.5109,0.0001</t>
+  </si>
+  <si>
+    <t>0.7369,0.0007,0.3740,0.0005</t>
+  </si>
+  <si>
+    <t>0.6258,0.0016,0.4688,0.0005</t>
+  </si>
+  <si>
+    <t>0.0071,0.4992,0.0236,0.8302</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.9916,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.0031,0.9864,0.0235,0.0001</t>
+  </si>
+  <si>
+    <t>0.5516,0.5145,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.7339,0.1035,0.0755,0.0006</t>
+  </si>
+  <si>
+    <t>0.7172,0.1425,0.0890,0.0010</t>
+  </si>
+  <si>
+    <t>0.9978,0.0014,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9957,0.0017,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0742,0.0852,0.8208,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.5927,0.9896,0.0000</t>
+  </si>
+  <si>
+    <t>0.0162,0.0039,0.9821,0.0001</t>
+  </si>
+  <si>
+    <t>0.0761,0.0063,0.9419,0.0001</t>
+  </si>
+  <si>
+    <t>0.9227,0.0006,0.0986,0.0001</t>
+  </si>
+  <si>
+    <t>0.8552,0.0070,0.1325,0.0008</t>
+  </si>
+  <si>
+    <t>0.6277,0.0001,0.6777,0.0000</t>
+  </si>
+  <si>
+    <t>0.8711,0.0004,0.1936,0.0002</t>
+  </si>
+  <si>
+    <t>0.5778,0.0063,0.1928,0.1236</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.0018,0.0006,0.9981</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0077,0.9983</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.8816,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9153,0.0606,0.0047,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.5401,0.4412,0.0093,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.4304,0.0001,0.4376,0.0102</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0306,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.9310,0.0001,0.0794,0.0002</t>
+  </si>
+  <si>
+    <t>0.9732,0.0008,0.0136,0.0004</t>
+  </si>
+  <si>
+    <t>0.8594,0.0182,0.0771,0.0005</t>
+  </si>
+  <si>
+    <t>0.9846,0.0015,0.0042,0.0001</t>
+  </si>
+  <si>
+    <t>0.9569,0.0017,0.0245,0.0001</t>
+  </si>
+  <si>
+    <t>0.4281,0.3095,0.0905,0.0041</t>
+  </si>
+  <si>
+    <t>0.8646,0.0021,0.1800,0.0002</t>
+  </si>
+  <si>
+    <t>0.9687,0.0024,0.0111,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
+    <t>0.9960,0.0016,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9806,0.0209,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9824,0.0047,0.0032,0.0001</t>
+  </si>
+  <si>
+    <t>0.9299,0.0417,0.0068,0.0001</t>
+  </si>
+  <si>
+    <t>0.1650,0.0203,0.8503,0.0011</t>
+  </si>
+  <si>
+    <t>0.9765,0.0299,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9898,0.0051,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9736,0.0149,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0156,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.8855,0.0209,0.0760,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.1968,0.0027,0.8632,0.0002</t>
+  </si>
+  <si>
+    <t>0.0164,0.0001,0.9951,0.0000</t>
+  </si>
+  <si>
+    <t>0.0215,0.0151,0.9572,0.0002</t>
+  </si>
+  <si>
+    <t>0.0076,0.0007,0.9929,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.0002,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.3641,0.0004,0.7899,0.0001</t>
+  </si>
+  <si>
+    <t>0.4653,0.0005,0.7520,0.0000</t>
+  </si>
+  <si>
+    <t>0.9044,0.0007,0.1230,0.0002</t>
+  </si>
+  <si>
+    <t>0.5298,0.0055,0.5734,0.0002</t>
+  </si>
+  <si>
+    <t>0.4700,0.0155,0.5414,0.0003</t>
+  </si>
+  <si>
+    <t>0.8790,0.0005,0.1921,0.0001</t>
+  </si>
+  <si>
+    <t>0.8796,0.0018,0.1260,0.0007</t>
+  </si>
+  <si>
+    <t>0.6021,0.0003,0.6477,0.0001</t>
+  </si>
+  <si>
+    <t>0.4753,0.6239,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.2294,0.8251,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9490,0.0576,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.8171,0.2462,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.4978,0.6354,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.4677,0.0007,0.7078,0.0001</t>
+  </si>
+  <si>
+    <t>0.9574,0.0001,0.0672,0.0000</t>
+  </si>
+  <si>
+    <t>0.9305,0.0002,0.0898,0.0002</t>
+  </si>
+  <si>
+    <t>0.8718,0.0010,0.1762,0.0002</t>
+  </si>
+  <si>
+    <t>0.6840,0.0003,0.5159,0.0001</t>
+  </si>
+  <si>
+    <t>0.0060,0.0002,0.9935,0.0004</t>
+  </si>
+  <si>
+    <t>0.0213,0.0081,0.9572,0.0021</t>
+  </si>
+  <si>
+    <t>0.3141,0.0038,0.7940,0.0001</t>
+  </si>
+  <si>
+    <t>0.0555,0.0019,0.9508,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.7602,0.7507,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9963,0.0039,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0016,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9830,0.0114,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0008,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9986,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9097,0.0002,0.1567,0.0000</t>
-  </si>
-  <si>
-    <t>0.2300,0.0002,0.8890,0.0001</t>
-  </si>
-  <si>
-    <t>0.8367,0.0003,0.3044,0.0000</t>
-  </si>
-  <si>
-    <t>0.0159,0.0005,0.9909,0.0000</t>
-  </si>
-  <si>
-    <t>0.9142,0.0002,0.1303,0.0001</t>
-  </si>
-  <si>
-    <t>0.0043,0.9941,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0241,0.9795,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.7959,0.1681,0.0102,0.0002</t>
-  </si>
-  <si>
-    <t>0.0517,0.9565,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0068,0.9936,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8994,0.0003,0.1493,0.0002</t>
-  </si>
-  <si>
-    <t>0.7850,0.0006,0.3170,0.0003</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.1136,0.0002,0.9383,0.0001</t>
-  </si>
-  <si>
-    <t>0.1864,0.0001,0.9086,0.0001</t>
-  </si>
-  <si>
-    <t>0.1173,0.0001,0.9555,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9992,0.0003</t>
-  </si>
-  <si>
-    <t>0.6203,0.3757,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.9694,0.0031,0.0119,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0016,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.1450,0.0976,0.5532,0.0001</t>
-  </si>
-  <si>
-    <t>0.9937,0.0005,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9002,0.0034,0.0797,0.0002</t>
-  </si>
-  <si>
-    <t>0.9272,0.0267,0.0164,0.0003</t>
-  </si>
-  <si>
-    <t>0.2580,0.5072,0.0917,0.0007</t>
-  </si>
-  <si>
-    <t>0.0010,0.9642,0.2753,0.0021</t>
-  </si>
-  <si>
-    <t>0.1314,0.0058,0.8612,0.0011</t>
-  </si>
-  <si>
-    <t>0.1011,0.0082,0.8984,0.0003</t>
-  </si>
-  <si>
-    <t>0.2264,0.0001,0.9241,0.0000</t>
-  </si>
-  <si>
-    <t>0.0445,0.0589,0.9329,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9970,0.0158,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.0005,0.9945,0.0001</t>
-  </si>
-  <si>
-    <t>0.6654,0.0465,0.2109,0.0210</t>
-  </si>
-  <si>
-    <t>0.0026,0.9933,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.9956,0.0045,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9988,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0022,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0287,0.0500,0.9230,0.0002</t>
-  </si>
-  <si>
-    <t>0.0838,0.0000,0.9573,0.0001</t>
-  </si>
-  <si>
-    <t>0.0040,0.0001,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0036,0.0008,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0011,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.9947,0.0057,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9461,0.0160,0.0172,0.0008</t>
-  </si>
-  <si>
-    <t>0.9892,0.0033,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.0031,0.0072,0.9950,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0058,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9965,0.0035,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.8615,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0015,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0231,0.0007,0.9827,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9869,0.9793,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.1681,0.8179,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6205,0.0009,0.5710,0.0001</t>
-  </si>
-  <si>
-    <t>0.6892,0.0003,0.5222,0.0001</t>
-  </si>
-  <si>
-    <t>0.0069,0.0133,0.9909,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9769,0.9375,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9654,0.3808,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9945,0.1608,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.4484,0.0000</t>
-  </si>
-  <si>
-    <t>0.0927,0.0002,0.8108,0.0297</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0004,0.9997</t>
-  </si>
-  <si>
-    <t>0.1222,0.0004,0.0018,0.9421</t>
-  </si>
-  <si>
-    <t>0.0060,0.0003,0.5294,0.8400</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.2993,0.9873</t>
-  </si>
-  <si>
-    <t>0.0030,0.0004,0.0261,0.9904</t>
-  </si>
-  <si>
-    <t>0.0001,0.9987,0.0462,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9911,0.5284,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9719,0.8991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.9461,0.3887,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.9830,0.4743,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9001,0.8046,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9895,0.0083,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9919,0.0100,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9924,0.0062,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0020,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0004,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0655,0.0006,0.9742,0.0000</t>
-  </si>
-  <si>
-    <t>0.9509,0.0007,0.0436,0.0001</t>
-  </si>
-  <si>
-    <t>0.5723,0.0002,0.7010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0089,0.9904,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.1105,0.8907,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.0552,0.9410,0.0046,0.0002</t>
-  </si>
-  <si>
-    <t>0.2475,0.7023,0.0244,0.0002</t>
-  </si>
-  <si>
-    <t>0.0103,0.9854,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8875,0.1423,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.7846,0.0004,0.3550,0.0001</t>
-  </si>
-  <si>
-    <t>0.8635,0.0009,0.1896,0.0001</t>
-  </si>
-  <si>
-    <t>0.6584,0.0019,0.4499,0.0004</t>
-  </si>
-  <si>
-    <t>0.9072,0.0005,0.1252,0.0001</t>
-  </si>
-  <si>
-    <t>0.2896,0.0383,0.1274,0.3680</t>
-  </si>
-  <si>
-    <t>0.0006,0.9981,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9985,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0054,0.9675,0.0592,0.0000</t>
-  </si>
-  <si>
-    <t>0.3556,0.7237,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9520,0.0127,0.0175,0.0004</t>
-  </si>
-  <si>
-    <t>0.8355,0.0738,0.0520,0.0007</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0011,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0190,0.0914,0.9236,0.0001</t>
-  </si>
-  <si>
-    <t>0.0025,0.4195,0.9480,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0019,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0291,0.0044,0.9710,0.0001</t>
-  </si>
-  <si>
-    <t>0.9718,0.0003,0.0240,0.0000</t>
-  </si>
-  <si>
-    <t>0.8812,0.0007,0.1691,0.0001</t>
-  </si>
-  <si>
-    <t>0.6717,0.0001,0.6481,0.0000</t>
-  </si>
-  <si>
-    <t>0.9538,0.0001,0.0637,0.0000</t>
-  </si>
-  <si>
-    <t>0.1413,0.0004,0.5166,0.1433</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0008,1.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0004,0.0002,0.9988</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0322,0.9968</t>
-  </si>
-  <si>
-    <t>0.0000,0.9966,0.6411,0.0000</t>
-  </si>
-  <si>
-    <t>0.9398,0.0415,0.0042,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8227,0.1604,0.0065,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.4785,0.0001,0.1594,0.0373</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0180,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.9007,0.0000,0.0593,0.0015</t>
-  </si>
-  <si>
-    <t>0.9811,0.0003,0.0068,0.0008</t>
-  </si>
-  <si>
-    <t>0.7499,0.0723,0.0737,0.0006</t>
-  </si>
-  <si>
-    <t>0.9885,0.0006,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.9737,0.0009,0.0134,0.0001</t>
-  </si>
-  <si>
-    <t>0.4317,0.1402,0.2114,0.0020</t>
-  </si>
-  <si>
-    <t>0.8697,0.0113,0.0816,0.0003</t>
-  </si>
-  <si>
-    <t>0.9855,0.0008,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0009,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9344,0.0887,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9207,0.0383,0.0118,0.0001</t>
-  </si>
-  <si>
-    <t>0.9271,0.0504,0.0056,0.0001</t>
-  </si>
-  <si>
-    <t>0.5300,0.0088,0.5940,0.0005</t>
-  </si>
-  <si>
-    <t>0.9911,0.0092,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9931,0.0017,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0014,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7621,0.2502,0.0066,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0144,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.9514,0.0092,0.0242,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0242,0.0051,0.9771,0.0001</t>
-  </si>
-  <si>
-    <t>0.0100,0.0001,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0184,0.0473,0.9406,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.0005,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0165,0.0002,0.9944,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.1319,0.0005,0.9051,0.0003</t>
-  </si>
-  <si>
-    <t>0.3140,0.0004,0.8726,0.0000</t>
-  </si>
-  <si>
-    <t>0.6732,0.0011,0.4686,0.0002</t>
-  </si>
-  <si>
-    <t>0.3310,0.0014,0.8017,0.0001</t>
-  </si>
-  <si>
-    <t>0.6501,0.0137,0.3576,0.0003</t>
-  </si>
-  <si>
-    <t>0.9591,0.0009,0.0311,0.0000</t>
-  </si>
-  <si>
-    <t>0.8460,0.0021,0.1655,0.0007</t>
-  </si>
-  <si>
-    <t>0.3043,0.0003,0.8601,0.0000</t>
-  </si>
-  <si>
-    <t>0.2979,0.7507,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.8281,0.1737,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.9172,0.0585,0.0064,0.0001</t>
-  </si>
-  <si>
-    <t>0.7931,0.2858,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.5790,0.5524,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8664,0.0007,0.2050,0.0001</t>
-  </si>
-  <si>
-    <t>0.9720,0.0003,0.0258,0.0000</t>
-  </si>
-  <si>
-    <t>0.8789,0.0003,0.1831,0.0002</t>
-  </si>
-  <si>
-    <t>0.9329,0.0010,0.0663,0.0001</t>
-  </si>
-  <si>
-    <t>0.9373,0.0002,0.0892,0.0001</t>
-  </si>
-  <si>
-    <t>0.0078,0.0001,0.9918,0.0005</t>
-  </si>
-  <si>
-    <t>0.0231,0.0072,0.9564,0.0013</t>
-  </si>
-  <si>
-    <t>0.0617,0.0061,0.9478,0.0002</t>
-  </si>
-  <si>
-    <t>0.0568,0.0031,0.9555,0.0001</t>
-  </si>
-  <si>
-    <t>0.0066,0.0514,0.9610,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0032,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9944,0.0067,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9934,0.0077,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9824,0.0069,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0016,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0008,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.4003,0.0249,0.5751,0.0010</t>
-  </si>
-  <si>
-    <t>0.9370,0.0003,0.0751,0.0001</t>
-  </si>
-  <si>
-    <t>0.0240,0.0002,0.9863,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0007,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.0401,0.0762,0.8590,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0001,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0344,0.0022,0.9781,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0008,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.2537,0.0015,0.8356,0.0001</t>
-  </si>
-  <si>
-    <t>0.0145,0.0012,0.9847,0.0002</t>
-  </si>
-  <si>
-    <t>0.8707,0.0003,0.2178,0.0001</t>
-  </si>
-  <si>
-    <t>0.9088,0.0001,0.1791,0.0000</t>
-  </si>
-  <si>
-    <t>0.9765,0.0002,0.0183,0.0001</t>
-  </si>
-  <si>
-    <t>0.9927,0.0064,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0029,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9950,0.0021,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9871,0.0061,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9937,0.0047,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9652,0.0340,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.2910,0.0123,0.6869,0.0004</t>
-  </si>
-  <si>
-    <t>0.0143,0.0020,0.9849,0.0001</t>
-  </si>
-  <si>
-    <t>0.0027,0.0006,0.9970,0.0001</t>
-  </si>
-  <si>
-    <t>0.1491,0.0128,0.8364,0.0002</t>
-  </si>
-  <si>
-    <t>0.0087,0.0011,0.9932,0.0001</t>
-  </si>
-  <si>
-    <t>0.2596,0.0002,0.8443,0.0003</t>
-  </si>
-  <si>
-    <t>0.1207,0.0006,0.9236,0.0002</t>
-  </si>
-  <si>
-    <t>0.0810,0.0004,0.9427,0.0003</t>
-  </si>
-  <si>
-    <t>0.9424,0.0003,0.0555,0.0005</t>
-  </si>
-  <si>
-    <t>0.7123,0.0037,0.0241,0.1417</t>
-  </si>
-  <si>
-    <t>0.1613,0.0007,0.6223,0.0871</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0161,0.9987</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0004,0.9997</t>
-  </si>
-  <si>
-    <t>0.9841,0.0002,0.0118,0.0001</t>
+    <t>0.0269,0.0002,0.9871,0.0001</t>
+  </si>
+  <si>
+    <t>0.3219,0.0408,0.6264,0.0012</t>
+  </si>
+  <si>
+    <t>0.9661,0.0004,0.0274,0.0002</t>
+  </si>
+  <si>
+    <t>0.0633,0.0006,0.9736,0.0000</t>
+  </si>
+  <si>
+    <t>0.0093,0.0026,0.9871,0.0003</t>
+  </si>
+  <si>
+    <t>0.1024,0.0279,0.8333,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0000,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.3404,0.0003,0.8137,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0131,0.0051,0.9778,0.0002</t>
+  </si>
+  <si>
+    <t>0.0011,0.0028,0.9979,0.0000</t>
+  </si>
+  <si>
+    <t>0.8215,0.0002,0.3188,0.0001</t>
+  </si>
+  <si>
+    <t>0.8133,0.0001,0.3546,0.0001</t>
+  </si>
+  <si>
+    <t>0.9544,0.0003,0.0536,0.0002</t>
+  </si>
+  <si>
+    <t>0.9867,0.0156,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9919,0.0056,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9963,0.0021,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9844,0.0131,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9932,0.0064,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9955,0.0017,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.1180,0.0078,0.8854,0.0001</t>
+  </si>
+  <si>
+    <t>0.0286,0.0101,0.9527,0.0002</t>
+  </si>
+  <si>
+    <t>0.0287,0.0029,0.9792,0.0000</t>
+  </si>
+  <si>
+    <t>0.3662,0.0203,0.6121,0.0013</t>
+  </si>
+  <si>
+    <t>0.0186,0.0002,0.9910,0.0000</t>
+  </si>
+  <si>
+    <t>0.2017,0.0005,0.8531,0.0009</t>
+  </si>
+  <si>
+    <t>0.3395,0.0008,0.8016,0.0001</t>
+  </si>
+  <si>
+    <t>0.2464,0.0008,0.8335,0.0004</t>
+  </si>
+  <si>
+    <t>0.9404,0.0002,0.0631,0.0004</t>
+  </si>
+  <si>
+    <t>0.7966,0.0058,0.0203,0.0936</t>
+  </si>
+  <si>
+    <t>0.1383,0.0008,0.2286,0.4817</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0024,0.9996</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0012,0.9996</t>
+  </si>
+  <si>
+    <t>0.9852,0.0003,0.0071,0.0002</t>
   </si>
 </sst>
 </file>
@@ -1920,7 +1932,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1931,10 +1943,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1948,7 +1960,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1959,10 +1971,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1976,7 +1988,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1990,7 +2002,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2018,7 +2030,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2074,7 +2086,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2088,7 +2100,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2102,7 +2114,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2116,7 +2128,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2130,7 +2142,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2144,7 +2156,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2158,7 +2170,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2172,7 +2184,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2186,7 +2198,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2200,7 +2212,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2214,7 +2226,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2228,7 +2240,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2242,7 +2254,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2256,7 +2268,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2270,7 +2282,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2284,7 +2296,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2298,7 +2310,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2312,7 +2324,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2326,7 +2338,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2340,7 +2352,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2354,7 +2366,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2365,10 +2377,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2382,7 +2394,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2393,10 +2405,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2410,7 +2422,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2421,10 +2433,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2438,7 +2450,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2449,10 +2461,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2466,7 +2478,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2477,10 +2489,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2494,7 +2506,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2508,7 +2520,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2522,7 +2534,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2533,10 +2545,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2550,7 +2562,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2564,7 +2576,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2578,7 +2590,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2592,7 +2604,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2606,7 +2618,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2620,7 +2632,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2634,7 +2646,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2648,7 +2660,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2662,7 +2674,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2676,7 +2688,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2690,7 +2702,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2704,7 +2716,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2718,7 +2730,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2732,7 +2744,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2746,7 +2758,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2760,7 +2772,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2774,7 +2786,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2788,7 +2800,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2802,7 +2814,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2816,7 +2828,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2830,7 +2842,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2844,7 +2856,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2858,7 +2870,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2869,10 +2881,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2883,10 +2895,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2900,7 +2912,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2914,7 +2926,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2928,7 +2940,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2942,7 +2954,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2956,7 +2968,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2967,10 +2979,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2984,7 +2996,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2998,7 +3010,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3009,10 +3021,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3026,7 +3038,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3040,7 +3052,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3054,7 +3066,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3068,7 +3080,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3082,7 +3094,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3093,10 +3105,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3107,10 +3119,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3124,7 +3136,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3138,7 +3150,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3152,7 +3164,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3166,7 +3178,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3180,7 +3192,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3194,7 +3206,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3208,7 +3220,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3222,7 +3234,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3250,7 +3262,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>359</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3264,7 +3276,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3292,7 +3304,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3306,7 +3318,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3320,7 +3332,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3334,7 +3346,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3348,7 +3360,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3362,7 +3374,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3376,7 +3388,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3390,7 +3402,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3404,7 +3416,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3418,7 +3430,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3432,7 +3444,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3446,7 +3458,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3460,7 +3472,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3474,7 +3486,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3488,7 +3500,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3502,7 +3514,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3513,10 +3525,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3527,10 +3539,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D117" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3544,7 +3556,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3558,7 +3570,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3569,10 +3581,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3586,7 +3598,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3600,7 +3612,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3614,7 +3626,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3628,7 +3640,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3639,10 +3651,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D125" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3656,7 +3668,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3670,7 +3682,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3684,7 +3696,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3698,7 +3710,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3712,7 +3724,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3726,7 +3738,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3740,7 +3752,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3754,7 +3766,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3768,7 +3780,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3782,7 +3794,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>392</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3807,7 +3819,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>394</v>
@@ -3877,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D142" t="s">
         <v>399</v>
@@ -3905,7 +3917,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D144" t="s">
         <v>401</v>
@@ -3978,7 +3990,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>273</v>
+        <v>406</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3992,7 +4004,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4006,7 +4018,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4020,7 +4032,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4034,7 +4046,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4045,10 +4057,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D154" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4062,7 +4074,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4076,7 +4088,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4090,7 +4102,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4104,7 +4116,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4118,7 +4130,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4132,7 +4144,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4146,7 +4158,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4157,10 +4169,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4174,7 +4186,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4188,7 +4200,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4202,7 +4214,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4216,7 +4228,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4230,7 +4242,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4244,7 +4256,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4258,7 +4270,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>272</v>
+        <v>425</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4272,7 +4284,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4286,7 +4298,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4300,7 +4312,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>271</v>
+        <v>428</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4314,7 +4326,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4328,7 +4340,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4342,7 +4354,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4356,7 +4368,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4370,7 +4382,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4384,7 +4396,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4398,7 +4410,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4412,7 +4424,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4426,7 +4438,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4440,7 +4452,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4454,7 +4466,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4468,7 +4480,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4482,7 +4494,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4496,7 +4508,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4510,7 +4522,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4524,7 +4536,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4538,7 +4550,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4552,7 +4564,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4566,7 +4578,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4580,7 +4592,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4591,10 +4603,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4605,10 +4617,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4622,7 +4634,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4636,7 +4648,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4647,10 +4659,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4664,7 +4676,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4675,10 +4687,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4692,7 +4704,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4706,7 +4718,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4720,7 +4732,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4731,10 +4743,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D203" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4748,7 +4760,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4762,7 +4774,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4776,7 +4788,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4787,10 +4799,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D207" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4804,7 +4816,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4818,7 +4830,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4832,7 +4844,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4846,7 +4858,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4857,10 +4869,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4874,7 +4886,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>465</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4888,7 +4900,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4902,7 +4914,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4916,7 +4928,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4930,7 +4942,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4944,7 +4956,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>470</v>
+        <v>273</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4958,7 +4970,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4972,7 +4984,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>388</v>
+        <v>474</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4986,7 +4998,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5000,7 +5012,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5014,7 +5026,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5028,7 +5040,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5042,7 +5054,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5056,7 +5068,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5070,7 +5082,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5084,7 +5096,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5098,7 +5110,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5112,7 +5124,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5126,7 +5138,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5140,7 +5152,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5154,7 +5166,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5168,7 +5180,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5182,7 +5194,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5196,7 +5208,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5210,7 +5222,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5224,7 +5236,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5238,7 +5250,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5252,7 +5264,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5266,7 +5278,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5280,7 +5292,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>388</v>
+        <v>496</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5294,7 +5306,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5308,7 +5320,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5322,7 +5334,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5336,7 +5348,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5350,7 +5362,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5364,7 +5376,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5378,7 +5390,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5392,7 +5404,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5406,7 +5418,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5420,7 +5432,7 @@
         <v>259</v>
       </c>
       <c r="D252" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5431,10 +5443,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D253" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5448,7 +5460,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5462,7 +5474,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5476,7 +5488,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
